--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_RMSEP.xlsx
@@ -453,55 +453,55 @@
         </is>
       </c>
       <c r="B2">
-        <v>23.47936179982776</v>
+        <v>23.47936180407328</v>
       </c>
       <c r="C2">
         <v>36.7783252635105</v>
       </c>
       <c r="D2">
-        <v>28.25677527384965</v>
+        <v>28.25677526734539</v>
       </c>
       <c r="E2">
-        <v>23.62393146363803</v>
+        <v>23.62393146726979</v>
       </c>
       <c r="F2">
-        <v>22.70884395372683</v>
+        <v>22.70884395349958</v>
       </c>
       <c r="G2">
-        <v>22.37350123445112</v>
+        <v>22.3735012379858</v>
       </c>
       <c r="H2">
-        <v>22.7656038839328</v>
+        <v>22.76560388406136</v>
       </c>
       <c r="I2">
-        <v>22.05782140378277</v>
+        <v>22.05782140459604</v>
       </c>
       <c r="J2">
-        <v>21.92155975146008</v>
+        <v>21.92155976930881</v>
       </c>
       <c r="K2">
-        <v>22.55024015281616</v>
+        <v>22.55024017814146</v>
       </c>
       <c r="L2">
-        <v>22.24582072836179</v>
+        <v>22.24582076989791</v>
       </c>
       <c r="M2">
-        <v>22.80961847129263</v>
+        <v>22.80961848918046</v>
       </c>
       <c r="N2">
-        <v>23.13085951550166</v>
+        <v>23.13085953238961</v>
       </c>
       <c r="O2">
-        <v>24.39420199430904</v>
+        <v>24.394201934821</v>
       </c>
       <c r="P2">
-        <v>26.00661440017483</v>
+        <v>26.00661446553497</v>
       </c>
       <c r="Q2">
-        <v>27.38000470279729</v>
+        <v>27.38000482911537</v>
       </c>
       <c r="R2">
-        <v>27.99177357246779</v>
+        <v>27.99177348176308</v>
       </c>
     </row>
     <row r="3">
@@ -511,55 +511,55 @@
         </is>
       </c>
       <c r="B3">
-        <v>23.2717955775616</v>
+        <v>23.27179557147898</v>
       </c>
       <c r="C3">
         <v>36.7783252635105</v>
       </c>
       <c r="D3">
-        <v>26.73229248942049</v>
+        <v>26.73229259788859</v>
       </c>
       <c r="E3">
-        <v>23.1301234718599</v>
+        <v>23.13012344976263</v>
       </c>
       <c r="F3">
-        <v>23.47972326849572</v>
+        <v>23.47972323814935</v>
       </c>
       <c r="G3">
-        <v>24.66771866951647</v>
+        <v>24.66771851689426</v>
       </c>
       <c r="H3">
-        <v>23.82910875232461</v>
+        <v>23.82910870614025</v>
       </c>
       <c r="I3">
-        <v>23.83094093948123</v>
+        <v>23.83094078507454</v>
       </c>
       <c r="J3">
-        <v>25.01781663408177</v>
+        <v>25.01781633236414</v>
       </c>
       <c r="K3">
-        <v>25.4716648375746</v>
+        <v>25.47166442745173</v>
       </c>
       <c r="L3">
-        <v>26.68624568951991</v>
+        <v>26.68624497589242</v>
       </c>
       <c r="M3">
-        <v>27.14791857375612</v>
+        <v>27.14791725769016</v>
       </c>
       <c r="N3">
-        <v>27.78449469665567</v>
+        <v>27.78449255687448</v>
       </c>
       <c r="O3">
-        <v>28.80245054738698</v>
+        <v>28.8024477668035</v>
       </c>
       <c r="P3">
-        <v>29.50270845883072</v>
+        <v>29.50270465386195</v>
       </c>
       <c r="Q3">
-        <v>29.53242163429784</v>
+        <v>29.53241786597226</v>
       </c>
       <c r="R3">
-        <v>29.11799223486617</v>
+        <v>29.11798834408776</v>
       </c>
     </row>
     <row r="4">
@@ -569,55 +569,55 @@
         </is>
       </c>
       <c r="B4">
-        <v>24.05317834941806</v>
+        <v>24.05317835036776</v>
       </c>
       <c r="C4">
         <v>36.7783252635105</v>
       </c>
       <c r="D4">
-        <v>27.71270193078872</v>
+        <v>27.71270192762209</v>
       </c>
       <c r="E4">
-        <v>23.95900755715674</v>
+        <v>23.95900756112623</v>
       </c>
       <c r="F4">
-        <v>23.68152186631388</v>
+        <v>23.68152186339831</v>
       </c>
       <c r="G4">
-        <v>23.34775001382525</v>
+        <v>23.34775001036544</v>
       </c>
       <c r="H4">
-        <v>23.04064602824906</v>
+        <v>23.04064605032697</v>
       </c>
       <c r="I4">
-        <v>21.96183929905626</v>
+        <v>21.96183938574412</v>
       </c>
       <c r="J4">
-        <v>21.88309525990694</v>
+        <v>21.88309531924329</v>
       </c>
       <c r="K4">
-        <v>22.19946555421401</v>
+        <v>22.19946561790364</v>
       </c>
       <c r="L4">
-        <v>22.74839691191801</v>
+        <v>22.74839704502971</v>
       </c>
       <c r="M4">
-        <v>23.483740310076</v>
+        <v>23.48374049850585</v>
       </c>
       <c r="N4">
-        <v>24.32671634569665</v>
+        <v>24.32671666251298</v>
       </c>
       <c r="O4">
-        <v>25.84163939444025</v>
+        <v>25.84163961930302</v>
       </c>
       <c r="P4">
-        <v>27.07427264268907</v>
+        <v>27.0742727480479</v>
       </c>
       <c r="Q4">
-        <v>27.92001816288029</v>
+        <v>27.92001820713771</v>
       </c>
       <c r="R4">
-        <v>28.73813408029118</v>
+        <v>28.73813382832218</v>
       </c>
     </row>
     <row r="5">
@@ -627,55 +627,55 @@
         </is>
       </c>
       <c r="B5">
-        <v>23.36070687700532</v>
+        <v>23.36070686890877</v>
       </c>
       <c r="C5">
         <v>36.7783252635105</v>
       </c>
       <c r="D5">
-        <v>23.31581082693482</v>
+        <v>23.31581081908759</v>
       </c>
       <c r="E5">
-        <v>23.09558476159108</v>
+        <v>23.09558474130582</v>
       </c>
       <c r="F5">
-        <v>22.91363443450608</v>
+        <v>22.91363441552768</v>
       </c>
       <c r="G5">
-        <v>23.02380749117621</v>
+        <v>23.0238074657881</v>
       </c>
       <c r="H5">
-        <v>22.79068374320356</v>
+        <v>22.79068368929005</v>
       </c>
       <c r="I5">
-        <v>22.84600379731672</v>
+        <v>22.84600371532622</v>
       </c>
       <c r="J5">
-        <v>23.35436707169353</v>
+        <v>23.35436700337599</v>
       </c>
       <c r="K5">
-        <v>24.54551568034869</v>
+        <v>24.54551550828583</v>
       </c>
       <c r="L5">
-        <v>26.41901902010221</v>
+        <v>26.4190190184177</v>
       </c>
       <c r="M5">
-        <v>27.37039749816571</v>
+        <v>27.37039763314572</v>
       </c>
       <c r="N5">
-        <v>28.17331415445262</v>
+        <v>28.17331431237877</v>
       </c>
       <c r="O5">
-        <v>28.26906889631009</v>
+        <v>28.26906895574136</v>
       </c>
       <c r="P5">
-        <v>28.10907982282071</v>
+        <v>28.1090796478629</v>
       </c>
       <c r="Q5">
-        <v>28.05355015124112</v>
+        <v>28.05354989450996</v>
       </c>
       <c r="R5">
-        <v>28.08766662340168</v>
+        <v>28.08766636668398</v>
       </c>
     </row>
     <row r="6">
@@ -685,55 +685,55 @@
         </is>
       </c>
       <c r="B6">
-        <v>23.54483530858528</v>
+        <v>23.54483529806313</v>
       </c>
       <c r="C6">
         <v>36.7783252635105</v>
       </c>
       <c r="D6">
-        <v>23.43250244036427</v>
+        <v>23.43250243264139</v>
       </c>
       <c r="E6">
-        <v>23.22781912041497</v>
+        <v>23.22781909247386</v>
       </c>
       <c r="F6">
-        <v>22.92846559019471</v>
+        <v>22.92846554945187</v>
       </c>
       <c r="G6">
-        <v>22.78362780411015</v>
+        <v>22.78362773945451</v>
       </c>
       <c r="H6">
-        <v>22.19011519674126</v>
+        <v>22.19011511080117</v>
       </c>
       <c r="I6">
-        <v>22.38370731565275</v>
+        <v>22.38370723768977</v>
       </c>
       <c r="J6">
-        <v>23.16055306545173</v>
+        <v>23.16055294346231</v>
       </c>
       <c r="K6">
-        <v>23.90285760486574</v>
+        <v>23.90285750901236</v>
       </c>
       <c r="L6">
-        <v>24.74372692490482</v>
+        <v>24.74372700118483</v>
       </c>
       <c r="M6">
-        <v>25.19797872222351</v>
+        <v>25.1979789361755</v>
       </c>
       <c r="N6">
-        <v>26.02795492257625</v>
+        <v>26.02795525491938</v>
       </c>
       <c r="O6">
-        <v>26.50531677819384</v>
+        <v>26.50531685446158</v>
       </c>
       <c r="P6">
-        <v>26.92223277679762</v>
+        <v>26.92223295573132</v>
       </c>
       <c r="Q6">
-        <v>27.0170524531357</v>
+        <v>27.0170524889494</v>
       </c>
       <c r="R6">
-        <v>27.31603019904911</v>
+        <v>27.31603012336472</v>
       </c>
     </row>
     <row r="7">
@@ -743,55 +743,55 @@
         </is>
       </c>
       <c r="B7">
-        <v>23.39097559023731</v>
+        <v>23.39097559249948</v>
       </c>
       <c r="C7">
         <v>36.7783252635105</v>
       </c>
       <c r="D7">
-        <v>27.65982932196518</v>
+        <v>27.65982931818869</v>
       </c>
       <c r="E7">
-        <v>23.6194372408333</v>
+        <v>23.6194372445317</v>
       </c>
       <c r="F7">
-        <v>22.18998494112573</v>
+        <v>22.18998494209591</v>
       </c>
       <c r="G7">
-        <v>21.94308674972849</v>
+        <v>21.94308674551704</v>
       </c>
       <c r="H7">
-        <v>21.92256028117234</v>
+        <v>21.92256027624448</v>
       </c>
       <c r="I7">
-        <v>21.64511187879291</v>
+        <v>21.64511189477068</v>
       </c>
       <c r="J7">
-        <v>21.93565590148425</v>
+        <v>21.93565594470904</v>
       </c>
       <c r="K7">
-        <v>21.89675551583464</v>
+        <v>21.89675560443411</v>
       </c>
       <c r="L7">
-        <v>22.3623168596387</v>
+        <v>22.3623169448436</v>
       </c>
       <c r="M7">
-        <v>23.06116408055109</v>
+        <v>23.06116427168864</v>
       </c>
       <c r="N7">
-        <v>23.77279513112846</v>
+        <v>23.77279548604873</v>
       </c>
       <c r="O7">
-        <v>25.36415868254067</v>
+        <v>25.36415910246795</v>
       </c>
       <c r="P7">
-        <v>26.50750293588183</v>
+        <v>26.50750319935112</v>
       </c>
       <c r="Q7">
-        <v>27.71924527517762</v>
+        <v>27.71924526495051</v>
       </c>
       <c r="R7">
-        <v>28.40603324638889</v>
+        <v>28.40603328095265</v>
       </c>
     </row>
     <row r="8">
@@ -801,55 +801,55 @@
         </is>
       </c>
       <c r="B8">
-        <v>23.53393140592127</v>
+        <v>23.53393140693519</v>
       </c>
       <c r="C8">
         <v>36.7783252635105</v>
       </c>
       <c r="D8">
-        <v>25.78138123984557</v>
+        <v>25.78138124450497</v>
       </c>
       <c r="E8">
-        <v>23.71224410704146</v>
+        <v>23.71224411148756</v>
       </c>
       <c r="F8">
-        <v>22.24928182432465</v>
+        <v>22.24928180941651</v>
       </c>
       <c r="G8">
-        <v>21.90182965176314</v>
+        <v>21.90182963903971</v>
       </c>
       <c r="H8">
-        <v>21.67890324724541</v>
+        <v>21.67890325447064</v>
       </c>
       <c r="I8">
-        <v>22.17979856559915</v>
+        <v>22.17979859650915</v>
       </c>
       <c r="J8">
-        <v>22.22556759793047</v>
+        <v>22.22556763957467</v>
       </c>
       <c r="K8">
-        <v>23.09431545939564</v>
+        <v>23.09431554572522</v>
       </c>
       <c r="L8">
-        <v>24.35021333916427</v>
+        <v>24.35021358243898</v>
       </c>
       <c r="M8">
-        <v>24.98238500557315</v>
+        <v>24.98238536285603</v>
       </c>
       <c r="N8">
-        <v>25.47480798269329</v>
+        <v>25.47480859711542</v>
       </c>
       <c r="O8">
-        <v>26.43581042765867</v>
+        <v>26.43581124848713</v>
       </c>
       <c r="P8">
-        <v>28.06582590484436</v>
+        <v>28.06582651798098</v>
       </c>
       <c r="Q8">
-        <v>29.21190612474481</v>
+        <v>29.21190636006076</v>
       </c>
       <c r="R8">
-        <v>29.90236329152732</v>
+        <v>29.90236320309872</v>
       </c>
     </row>
     <row r="9">
@@ -859,55 +859,55 @@
         </is>
       </c>
       <c r="B9">
-        <v>23.52718521722961</v>
+        <v>23.52718521680001</v>
       </c>
       <c r="C9">
         <v>36.7783252635105</v>
       </c>
       <c r="D9">
-        <v>25.81549343942005</v>
+        <v>25.81549344399123</v>
       </c>
       <c r="E9">
-        <v>23.78134148248057</v>
+        <v>23.78134148689133</v>
       </c>
       <c r="F9">
-        <v>22.31708793475688</v>
+        <v>22.31708792029996</v>
       </c>
       <c r="G9">
-        <v>21.90666932858417</v>
+        <v>21.90666931464622</v>
       </c>
       <c r="H9">
-        <v>21.58081863083466</v>
+        <v>21.58081864312342</v>
       </c>
       <c r="I9">
-        <v>21.94283543883008</v>
+        <v>21.94283546581955</v>
       </c>
       <c r="J9">
-        <v>21.88133166841511</v>
+        <v>21.88133169883036</v>
       </c>
       <c r="K9">
-        <v>22.12179571661925</v>
+        <v>22.12179576392569</v>
       </c>
       <c r="L9">
-        <v>22.7545906890131</v>
+        <v>22.75459078129503</v>
       </c>
       <c r="M9">
-        <v>23.15439044426712</v>
+        <v>23.1543906093846</v>
       </c>
       <c r="N9">
-        <v>23.1789632322234</v>
+        <v>23.17896374648262</v>
       </c>
       <c r="O9">
-        <v>23.5017780996801</v>
+        <v>23.50177872759273</v>
       </c>
       <c r="P9">
-        <v>24.34887723415384</v>
+        <v>24.34887796875984</v>
       </c>
       <c r="Q9">
-        <v>24.82435995276465</v>
+        <v>24.8243608703685</v>
       </c>
       <c r="R9">
-        <v>25.31395596960535</v>
+        <v>25.31395701436464</v>
       </c>
     </row>
     <row r="10">
@@ -917,55 +917,55 @@
         </is>
       </c>
       <c r="B10">
-        <v>23.47163699863147</v>
+        <v>23.47163699793424</v>
       </c>
       <c r="C10">
         <v>36.7783252635105</v>
       </c>
       <c r="D10">
-        <v>25.76083554910897</v>
+        <v>25.76083555376685</v>
       </c>
       <c r="E10">
-        <v>23.7322319048982</v>
+        <v>23.73223190925558</v>
       </c>
       <c r="F10">
-        <v>22.2809048808448</v>
+        <v>22.28090486595553</v>
       </c>
       <c r="G10">
-        <v>21.87029309239944</v>
+        <v>21.87029307898137</v>
       </c>
       <c r="H10">
-        <v>21.6142275639812</v>
+        <v>21.61422757378801</v>
       </c>
       <c r="I10">
-        <v>21.97449485060585</v>
+        <v>21.9744948749888</v>
       </c>
       <c r="J10">
-        <v>21.886262984302</v>
+        <v>21.88626301252785</v>
       </c>
       <c r="K10">
-        <v>22.09640952512181</v>
+        <v>22.09640957376618</v>
       </c>
       <c r="L10">
-        <v>22.6627632092852</v>
+        <v>22.66276327791963</v>
       </c>
       <c r="M10">
-        <v>23.02881120541415</v>
+        <v>23.02881139306741</v>
       </c>
       <c r="N10">
-        <v>23.04365911379156</v>
+        <v>23.04365958528609</v>
       </c>
       <c r="O10">
-        <v>23.35473207742593</v>
+        <v>23.35473286563528</v>
       </c>
       <c r="P10">
-        <v>24.23670951606664</v>
+        <v>24.23671042583342</v>
       </c>
       <c r="Q10">
-        <v>24.80076864372196</v>
+        <v>24.80076950449772</v>
       </c>
       <c r="R10">
-        <v>25.44689490386961</v>
+        <v>25.4468960698928</v>
       </c>
     </row>
     <row r="11">
@@ -975,55 +975,55 @@
         </is>
       </c>
       <c r="B11">
-        <v>23.49204404893672</v>
+        <v>23.49204404831875</v>
       </c>
       <c r="C11">
         <v>36.7783252635105</v>
       </c>
       <c r="D11">
-        <v>25.77177306819435</v>
+        <v>25.77177307283957</v>
       </c>
       <c r="E11">
-        <v>23.67023109429435</v>
+        <v>23.67023109869761</v>
       </c>
       <c r="F11">
-        <v>22.21003383833665</v>
+        <v>22.21003382372495</v>
       </c>
       <c r="G11">
-        <v>21.84557749756222</v>
+        <v>21.84557748408356</v>
       </c>
       <c r="H11">
-        <v>21.56438952988126</v>
+        <v>21.56438953991269</v>
       </c>
       <c r="I11">
-        <v>21.89938171511885</v>
+        <v>21.89938174861254</v>
       </c>
       <c r="J11">
-        <v>21.85284626699696</v>
+        <v>21.85284631779621</v>
       </c>
       <c r="K11">
-        <v>22.00594440795632</v>
+        <v>22.00594448616762</v>
       </c>
       <c r="L11">
-        <v>22.53911029349756</v>
+        <v>22.53911044121218</v>
       </c>
       <c r="M11">
-        <v>22.657102642175</v>
+        <v>22.65710289069208</v>
       </c>
       <c r="N11">
-        <v>22.63955681828047</v>
+        <v>22.63955725870131</v>
       </c>
       <c r="O11">
-        <v>22.86106996090964</v>
+        <v>22.86107070225898</v>
       </c>
       <c r="P11">
-        <v>23.72394573679263</v>
+        <v>23.72394661426948</v>
       </c>
       <c r="Q11">
-        <v>24.35863666409486</v>
+        <v>24.35863760571567</v>
       </c>
       <c r="R11">
-        <v>24.76059892360055</v>
+        <v>24.76059995851732</v>
       </c>
     </row>
     <row r="12">
@@ -1033,55 +1033,55 @@
         </is>
       </c>
       <c r="B12">
-        <v>22.88304891629113</v>
+        <v>22.88304890526039</v>
       </c>
       <c r="C12">
         <v>36.7783252635105</v>
       </c>
       <c r="D12">
-        <v>22.89700744565065</v>
+        <v>22.89700743566843</v>
       </c>
       <c r="E12">
-        <v>22.60157923288419</v>
+        <v>22.60157920635554</v>
       </c>
       <c r="F12">
-        <v>22.36990954474219</v>
+        <v>22.36990951436889</v>
       </c>
       <c r="G12">
-        <v>22.34741533722841</v>
+        <v>22.34741529334633</v>
       </c>
       <c r="H12">
-        <v>22.27320712257797</v>
+        <v>22.27320704878874</v>
       </c>
       <c r="I12">
-        <v>22.28145630259184</v>
+        <v>22.28145620363806</v>
       </c>
       <c r="J12">
-        <v>22.88827312335227</v>
+        <v>22.88827299924593</v>
       </c>
       <c r="K12">
-        <v>24.05371346133022</v>
+        <v>24.05371328650001</v>
       </c>
       <c r="L12">
-        <v>25.77243731338686</v>
+        <v>25.77243722345679</v>
       </c>
       <c r="M12">
-        <v>27.25405175591855</v>
+        <v>27.25405179305302</v>
       </c>
       <c r="N12">
-        <v>28.860632189161</v>
+        <v>28.86063216652174</v>
       </c>
       <c r="O12">
-        <v>29.45864253752315</v>
+        <v>29.45864241842154</v>
       </c>
       <c r="P12">
-        <v>29.28652664676022</v>
+        <v>29.28652657405198</v>
       </c>
       <c r="Q12">
-        <v>29.15260936891794</v>
+        <v>29.1526094620118</v>
       </c>
       <c r="R12">
-        <v>29.70701160726849</v>
+        <v>29.70701202125428</v>
       </c>
     </row>
     <row r="13">
@@ -1091,55 +1091,55 @@
         </is>
       </c>
       <c r="B13">
-        <v>23.00901520072983</v>
+        <v>23.00901519834288</v>
       </c>
       <c r="C13">
         <v>36.7783252635105</v>
       </c>
       <c r="D13">
-        <v>22.99345687451578</v>
+        <v>22.99345687273329</v>
       </c>
       <c r="E13">
-        <v>23.09043247035899</v>
+        <v>23.09043245762025</v>
       </c>
       <c r="F13">
-        <v>22.72935286314836</v>
+        <v>22.72935284958584</v>
       </c>
       <c r="G13">
-        <v>22.40662325473617</v>
+        <v>22.40662322365432</v>
       </c>
       <c r="H13">
-        <v>23.55894469529022</v>
+        <v>23.55894467386219</v>
       </c>
       <c r="I13">
-        <v>24.09916932517081</v>
+        <v>24.09916915192431</v>
       </c>
       <c r="J13">
-        <v>24.12570763341241</v>
+        <v>24.1257074298578</v>
       </c>
       <c r="K13">
-        <v>24.49952459363621</v>
+        <v>24.4995244760635</v>
       </c>
       <c r="L13">
-        <v>26.37827172569118</v>
+        <v>26.37827135195021</v>
       </c>
       <c r="M13">
-        <v>27.98693603588389</v>
+        <v>27.9869359697368</v>
       </c>
       <c r="N13">
-        <v>28.5365199121314</v>
+        <v>28.53651991117415</v>
       </c>
       <c r="O13">
-        <v>28.56303224880342</v>
+        <v>28.56303219811656</v>
       </c>
       <c r="P13">
-        <v>29.08795354073128</v>
+        <v>29.08795365431898</v>
       </c>
       <c r="Q13">
-        <v>29.2182888038573</v>
+        <v>29.21828863082761</v>
       </c>
       <c r="R13">
-        <v>29.98225553056636</v>
+        <v>29.98225492317958</v>
       </c>
     </row>
     <row r="14">
@@ -1149,55 +1149,55 @@
         </is>
       </c>
       <c r="B14">
-        <v>23.42021443921109</v>
+        <v>23.42021444099208</v>
       </c>
       <c r="C14">
         <v>36.7783252635105</v>
       </c>
       <c r="D14">
-        <v>27.60606589490132</v>
+        <v>27.60606589124647</v>
       </c>
       <c r="E14">
-        <v>23.64466095584059</v>
+        <v>23.64466095908183</v>
       </c>
       <c r="F14">
-        <v>22.26349513952713</v>
+        <v>22.26349513978322</v>
       </c>
       <c r="G14">
-        <v>21.97191101103775</v>
+        <v>21.97191100605824</v>
       </c>
       <c r="H14">
-        <v>21.94418793014658</v>
+        <v>21.94418792458067</v>
       </c>
       <c r="I14">
-        <v>21.51143818163562</v>
+        <v>21.5114381969727</v>
       </c>
       <c r="J14">
-        <v>21.87188628809542</v>
+        <v>21.87188632858232</v>
       </c>
       <c r="K14">
-        <v>21.75857472513464</v>
+        <v>21.7585748008359</v>
       </c>
       <c r="L14">
-        <v>21.90370462002536</v>
+        <v>21.90370469573387</v>
       </c>
       <c r="M14">
-        <v>22.30331961791545</v>
+        <v>22.30331977132392</v>
       </c>
       <c r="N14">
-        <v>22.4087906465057</v>
+        <v>22.40879041794375</v>
       </c>
       <c r="O14">
-        <v>23.13311734908687</v>
+        <v>23.13312317019974</v>
       </c>
       <c r="P14">
-        <v>23.91885706162042</v>
+        <v>23.91885820366855</v>
       </c>
       <c r="Q14">
-        <v>24.94812562043692</v>
+        <v>24.94812655154487</v>
       </c>
       <c r="R14">
-        <v>26.21645496382816</v>
+        <v>26.21645564217529</v>
       </c>
     </row>
     <row r="15">
@@ -1207,55 +1207,55 @@
         </is>
       </c>
       <c r="B15">
-        <v>23.41323295937379</v>
+        <v>23.41323296228076</v>
       </c>
       <c r="C15">
         <v>36.7783252635105</v>
       </c>
       <c r="D15">
-        <v>27.59170027590058</v>
+        <v>27.59170027229619</v>
       </c>
       <c r="E15">
-        <v>23.59413662465715</v>
+        <v>23.5941366279579</v>
       </c>
       <c r="F15">
-        <v>22.21786788141292</v>
+        <v>22.21786788077658</v>
       </c>
       <c r="G15">
-        <v>21.97131201498312</v>
+        <v>21.97131200907974</v>
       </c>
       <c r="H15">
-        <v>21.92415320054153</v>
+        <v>21.92415319564102</v>
       </c>
       <c r="I15">
-        <v>21.68077781262449</v>
+        <v>21.68077782806868</v>
       </c>
       <c r="J15">
-        <v>21.87381079191639</v>
+        <v>21.87381083337904</v>
       </c>
       <c r="K15">
-        <v>21.7221236021629</v>
+        <v>21.72212367662943</v>
       </c>
       <c r="L15">
-        <v>21.68622426195142</v>
+        <v>21.68622433202991</v>
       </c>
       <c r="M15">
-        <v>22.13685262361262</v>
+        <v>22.1368526966992</v>
       </c>
       <c r="N15">
-        <v>22.27251032691699</v>
+        <v>22.27251044828548</v>
       </c>
       <c r="O15">
-        <v>22.93153936470334</v>
+        <v>22.93153970438491</v>
       </c>
       <c r="P15">
-        <v>23.87447966338266</v>
+        <v>23.87448034282295</v>
       </c>
       <c r="Q15">
-        <v>24.48465100593403</v>
+        <v>24.48465186035787</v>
       </c>
       <c r="R15">
-        <v>24.87294640495942</v>
+        <v>24.87294730792258</v>
       </c>
     </row>
     <row r="16">
@@ -1265,55 +1265,55 @@
         </is>
       </c>
       <c r="B16">
-        <v>23.38569913701723</v>
+        <v>23.38569913928153</v>
       </c>
       <c r="C16">
         <v>36.7783252635105</v>
       </c>
       <c r="D16">
-        <v>27.55013953430371</v>
+        <v>27.55013953036375</v>
       </c>
       <c r="E16">
-        <v>23.57626920252729</v>
+        <v>23.57626920582006</v>
       </c>
       <c r="F16">
-        <v>22.15158784839401</v>
+        <v>22.15158784876487</v>
       </c>
       <c r="G16">
-        <v>21.88742173820344</v>
+        <v>21.88742173297967</v>
       </c>
       <c r="H16">
-        <v>21.85556703820013</v>
+        <v>21.85556703485312</v>
       </c>
       <c r="I16">
-        <v>21.48473298142548</v>
+        <v>21.48473299901772</v>
       </c>
       <c r="J16">
-        <v>21.80813661634943</v>
+        <v>21.80813666239321</v>
       </c>
       <c r="K16">
-        <v>21.72594072811846</v>
+        <v>21.72594081317169</v>
       </c>
       <c r="L16">
-        <v>21.86229268593325</v>
+        <v>21.86229278093329</v>
       </c>
       <c r="M16">
-        <v>22.236299124814</v>
+        <v>22.23629924965807</v>
       </c>
       <c r="N16">
-        <v>22.35968841805719</v>
+        <v>22.35968805993505</v>
       </c>
       <c r="O16">
-        <v>23.27933794412284</v>
+        <v>23.27934121961515</v>
       </c>
       <c r="P16">
-        <v>24.38892326810109</v>
+        <v>24.38892585977937</v>
       </c>
       <c r="Q16">
-        <v>25.1722732278754</v>
+        <v>25.17227418393435</v>
       </c>
       <c r="R16">
-        <v>25.45765798310528</v>
+        <v>25.45765907061669</v>
       </c>
     </row>
     <row r="17">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="B17">
-        <v>23.51267073655991</v>
+        <v>23.51267074021806</v>
       </c>
       <c r="C17">
         <v>36.7783252635105</v>
       </c>
       <c r="D17">
-        <v>27.61975331949987</v>
+        <v>27.61975331570352</v>
       </c>
       <c r="E17">
-        <v>23.6145049643131</v>
+        <v>23.61450496777763</v>
       </c>
       <c r="F17">
-        <v>22.20936542526425</v>
+        <v>22.20936542524916</v>
       </c>
       <c r="G17">
-        <v>21.93797437188601</v>
+        <v>21.93797436692451</v>
       </c>
       <c r="H17">
-        <v>21.90046353852195</v>
+        <v>21.90046353509702</v>
       </c>
       <c r="I17">
-        <v>21.58546381954101</v>
+        <v>21.58546383252595</v>
       </c>
       <c r="J17">
-        <v>21.76249050031661</v>
+        <v>21.76249054231277</v>
       </c>
       <c r="K17">
-        <v>21.65854282711069</v>
+        <v>21.65854289922422</v>
       </c>
       <c r="L17">
-        <v>21.78464296283326</v>
+        <v>21.78464304005697</v>
       </c>
       <c r="M17">
-        <v>22.10938132253519</v>
+        <v>22.10938143808346</v>
       </c>
       <c r="N17">
-        <v>22.20434947739927</v>
+        <v>22.20434966271311</v>
       </c>
       <c r="O17">
-        <v>23.09612588883173</v>
+        <v>23.09612627339046</v>
       </c>
       <c r="P17">
-        <v>24.07303430913865</v>
+        <v>24.07303516358704</v>
       </c>
       <c r="Q17">
-        <v>24.95160860784868</v>
+        <v>24.95160979000925</v>
       </c>
       <c r="R17">
-        <v>25.13242046733274</v>
+        <v>25.13242153624124</v>
       </c>
     </row>
     <row r="18">
@@ -1381,55 +1381,55 @@
         </is>
       </c>
       <c r="B18">
-        <v>22.93002023258162</v>
+        <v>22.93002022252789</v>
       </c>
       <c r="C18">
         <v>36.7783252635105</v>
       </c>
       <c r="D18">
-        <v>22.90516967387523</v>
+        <v>22.90516966452478</v>
       </c>
       <c r="E18">
-        <v>22.65972778016634</v>
+        <v>22.65972775720069</v>
       </c>
       <c r="F18">
-        <v>22.53516786912764</v>
+        <v>22.53516784624815</v>
       </c>
       <c r="G18">
-        <v>22.62887294912777</v>
+        <v>22.62887291749487</v>
       </c>
       <c r="H18">
-        <v>22.29499805086678</v>
+        <v>22.29499799293087</v>
       </c>
       <c r="I18">
-        <v>22.71265358093166</v>
+        <v>22.71265349516694</v>
       </c>
       <c r="J18">
-        <v>23.06402160834019</v>
+        <v>23.06402148563959</v>
       </c>
       <c r="K18">
-        <v>24.05604849232914</v>
+        <v>24.05604838061425</v>
       </c>
       <c r="L18">
-        <v>25.53244051187466</v>
+        <v>25.53244038514083</v>
       </c>
       <c r="M18">
-        <v>26.93647133749117</v>
+        <v>26.93647139017809</v>
       </c>
       <c r="N18">
-        <v>28.12088341926346</v>
+        <v>28.12088346657677</v>
       </c>
       <c r="O18">
-        <v>28.66611935089072</v>
+        <v>28.66611929878208</v>
       </c>
       <c r="P18">
-        <v>28.60670630005903</v>
+        <v>28.60670606825984</v>
       </c>
       <c r="Q18">
-        <v>28.54419198370611</v>
+        <v>28.54419168132018</v>
       </c>
       <c r="R18">
-        <v>28.4958307833114</v>
+        <v>28.49583027500374</v>
       </c>
     </row>
     <row r="19">
@@ -1439,55 +1439,55 @@
         </is>
       </c>
       <c r="B19">
-        <v>22.88617254897265</v>
+        <v>22.88617253573263</v>
       </c>
       <c r="C19">
         <v>36.7783252635105</v>
       </c>
       <c r="D19">
-        <v>22.9430415393879</v>
+        <v>22.94304152974073</v>
       </c>
       <c r="E19">
-        <v>22.6793157246678</v>
+        <v>22.67931569106611</v>
       </c>
       <c r="F19">
-        <v>22.30516907960531</v>
+        <v>22.30516903381145</v>
       </c>
       <c r="G19">
-        <v>22.10655515757632</v>
+        <v>22.10655509429925</v>
       </c>
       <c r="H19">
-        <v>21.58192551259063</v>
+        <v>21.58192543834575</v>
       </c>
       <c r="I19">
-        <v>22.28802887224624</v>
+        <v>22.28802878301613</v>
       </c>
       <c r="J19">
-        <v>22.31018242922438</v>
+        <v>22.3101823584862</v>
       </c>
       <c r="K19">
-        <v>23.10108851053826</v>
+        <v>23.10108843252641</v>
       </c>
       <c r="L19">
-        <v>23.95846370923473</v>
+        <v>23.95846370822508</v>
       </c>
       <c r="M19">
-        <v>24.97324740068089</v>
+        <v>24.9732475997866</v>
       </c>
       <c r="N19">
-        <v>25.91170996561246</v>
+        <v>25.91171019757588</v>
       </c>
       <c r="O19">
-        <v>26.45919657665976</v>
+        <v>26.45919664550242</v>
       </c>
       <c r="P19">
-        <v>27.03156649998978</v>
+        <v>27.03156635459789</v>
       </c>
       <c r="Q19">
-        <v>27.28029391838836</v>
+        <v>27.28029353780907</v>
       </c>
       <c r="R19">
-        <v>27.72987483727537</v>
+        <v>27.72987398287913</v>
       </c>
     </row>
     <row r="20">
@@ -1497,55 +1497,55 @@
         </is>
       </c>
       <c r="B20">
-        <v>22.97406102832392</v>
+        <v>22.97406101924467</v>
       </c>
       <c r="C20">
         <v>36.7783252635105</v>
       </c>
       <c r="D20">
-        <v>22.96490732064066</v>
+        <v>22.96490731466415</v>
       </c>
       <c r="E20">
-        <v>22.51573262260802</v>
+        <v>22.51573259749283</v>
       </c>
       <c r="F20">
-        <v>21.97081063064355</v>
+        <v>21.97081058896649</v>
       </c>
       <c r="G20">
-        <v>21.90573259404525</v>
+        <v>21.90573254436877</v>
       </c>
       <c r="H20">
-        <v>21.55522011534194</v>
+        <v>21.55522007588914</v>
       </c>
       <c r="I20">
-        <v>21.55098299062412</v>
+        <v>21.55098296764943</v>
       </c>
       <c r="J20">
-        <v>22.0239883648014</v>
+        <v>22.0239882803284</v>
       </c>
       <c r="K20">
-        <v>22.9210410251444</v>
+        <v>22.92104110347071</v>
       </c>
       <c r="L20">
-        <v>23.57048488950909</v>
+        <v>23.57048524518121</v>
       </c>
       <c r="M20">
-        <v>23.89414666110813</v>
+        <v>23.89414700918949</v>
       </c>
       <c r="N20">
-        <v>24.64305588180323</v>
+        <v>24.64305642576057</v>
       </c>
       <c r="O20">
-        <v>25.210933524989</v>
+        <v>25.21093407051527</v>
       </c>
       <c r="P20">
-        <v>25.3413645197961</v>
+        <v>25.34136484988977</v>
       </c>
       <c r="Q20">
-        <v>25.93297678088353</v>
+        <v>25.93297659719411</v>
       </c>
       <c r="R20">
-        <v>26.45152686799232</v>
+        <v>26.45152584906034</v>
       </c>
     </row>
     <row r="21">
@@ -1555,55 +1555,55 @@
         </is>
       </c>
       <c r="B21">
-        <v>23.47506551945678</v>
+        <v>23.47506552306848</v>
       </c>
       <c r="C21">
         <v>36.7783252635105</v>
       </c>
       <c r="D21">
-        <v>26.78942463160896</v>
+        <v>26.78942474889375</v>
       </c>
       <c r="E21">
-        <v>23.27975194712953</v>
+        <v>23.27975193378632</v>
       </c>
       <c r="F21">
-        <v>23.68551136539971</v>
+        <v>23.68551134883124</v>
       </c>
       <c r="G21">
-        <v>24.79598854105599</v>
+        <v>24.79598843195637</v>
       </c>
       <c r="H21">
-        <v>23.90445916029439</v>
+        <v>23.90445918096359</v>
       </c>
       <c r="I21">
-        <v>24.22428109623043</v>
+        <v>24.22428114485273</v>
       </c>
       <c r="J21">
-        <v>25.78591288719219</v>
+        <v>25.78591276022516</v>
       </c>
       <c r="K21">
-        <v>27.42094788180254</v>
+        <v>27.42094787553187</v>
       </c>
       <c r="L21">
-        <v>27.88834621851845</v>
+        <v>27.88834634257059</v>
       </c>
       <c r="M21">
-        <v>28.6913723288981</v>
+        <v>28.69137250725412</v>
       </c>
       <c r="N21">
-        <v>28.97248457623677</v>
+        <v>28.97248441877643</v>
       </c>
       <c r="O21">
-        <v>29.1629788123382</v>
+        <v>29.16297788357895</v>
       </c>
       <c r="P21">
-        <v>29.15534306742411</v>
+        <v>29.15534154495304</v>
       </c>
       <c r="Q21">
-        <v>28.98013743699961</v>
+        <v>28.98013616791956</v>
       </c>
       <c r="R21">
-        <v>29.35646368834329</v>
+        <v>29.35646270202353</v>
       </c>
     </row>
     <row r="22">
@@ -1613,55 +1613,55 @@
         </is>
       </c>
       <c r="B22">
-        <v>23.41930943252927</v>
+        <v>23.41930943027561</v>
       </c>
       <c r="C22">
         <v>36.7783252635105</v>
       </c>
       <c r="D22">
-        <v>26.81148537458581</v>
+        <v>26.81148549121632</v>
       </c>
       <c r="E22">
-        <v>23.26535551224678</v>
+        <v>23.26535549842227</v>
       </c>
       <c r="F22">
-        <v>23.62417904699555</v>
+        <v>23.62417903176148</v>
       </c>
       <c r="G22">
-        <v>24.89863637681983</v>
+        <v>24.89863626252833</v>
       </c>
       <c r="H22">
-        <v>23.81089272910262</v>
+        <v>23.81089273653851</v>
       </c>
       <c r="I22">
-        <v>23.7946602631421</v>
+        <v>23.79466044641018</v>
       </c>
       <c r="J22">
-        <v>25.53248809087905</v>
+        <v>25.53248793278602</v>
       </c>
       <c r="K22">
-        <v>26.94566064617943</v>
+        <v>26.94566031029102</v>
       </c>
       <c r="L22">
-        <v>27.71039427757603</v>
+        <v>27.71039364235025</v>
       </c>
       <c r="M22">
-        <v>28.09895045042226</v>
+        <v>28.09894936732792</v>
       </c>
       <c r="N22">
-        <v>28.73921587843889</v>
+        <v>28.73921420832135</v>
       </c>
       <c r="O22">
-        <v>28.82217457648393</v>
+        <v>28.82217089889605</v>
       </c>
       <c r="P22">
-        <v>28.71138884369403</v>
+        <v>28.71138415619367</v>
       </c>
       <c r="Q22">
-        <v>28.65798570068539</v>
+        <v>28.65798045111059</v>
       </c>
       <c r="R22">
-        <v>29.36832966913992</v>
+        <v>29.36832426027894</v>
       </c>
     </row>
     <row r="23">
@@ -1671,55 +1671,55 @@
         </is>
       </c>
       <c r="B23">
-        <v>23.08224982213964</v>
+        <v>23.08224983121686</v>
       </c>
       <c r="C23">
         <v>36.7783252635105</v>
       </c>
       <c r="D23">
-        <v>23.08224982213964</v>
+        <v>23.08224983121686</v>
       </c>
       <c r="E23">
-        <v>23.13723052455438</v>
+        <v>23.13723052785045</v>
       </c>
       <c r="F23">
-        <v>23.70027765998368</v>
+        <v>23.70027763250533</v>
       </c>
       <c r="G23">
-        <v>23.06154718274425</v>
+        <v>23.06154723684969</v>
       </c>
       <c r="H23">
-        <v>24.68783372707723</v>
+        <v>24.68783517305369</v>
       </c>
       <c r="I23">
-        <v>26.07134598977085</v>
+        <v>26.07134627445735</v>
       </c>
       <c r="J23">
-        <v>27.55295605841863</v>
+        <v>27.5529568695391</v>
       </c>
       <c r="K23">
-        <v>27.97418375021152</v>
+        <v>27.97418502429809</v>
       </c>
       <c r="L23">
-        <v>27.63461971491568</v>
+        <v>27.63462148089881</v>
       </c>
       <c r="M23">
-        <v>28.63561277880749</v>
+        <v>28.63561503055276</v>
       </c>
       <c r="N23">
-        <v>29.2169474568577</v>
+        <v>29.21695206203162</v>
       </c>
       <c r="O23">
-        <v>29.7355990302515</v>
+        <v>29.73560673961908</v>
       </c>
       <c r="P23">
-        <v>30.28575896325516</v>
+        <v>30.28576999199843</v>
       </c>
       <c r="Q23">
-        <v>30.540944329852</v>
+        <v>30.54095703458973</v>
       </c>
       <c r="R23">
-        <v>31.17797726601507</v>
+        <v>31.17799332022113</v>
       </c>
     </row>
     <row r="24">
@@ -1729,55 +1729,55 @@
         </is>
       </c>
       <c r="B24">
-        <v>23.19619883619035</v>
+        <v>23.19619883157998</v>
       </c>
       <c r="C24">
         <v>36.7783252635105</v>
       </c>
       <c r="D24">
-        <v>23.23124185629132</v>
+        <v>23.23124185559629</v>
       </c>
       <c r="E24">
-        <v>22.28736723990458</v>
+        <v>22.28736724256146</v>
       </c>
       <c r="F24">
-        <v>22.99235100395869</v>
+        <v>22.99235099575919</v>
       </c>
       <c r="G24">
-        <v>22.42993328764484</v>
+        <v>22.42993329652992</v>
       </c>
       <c r="H24">
-        <v>22.52876063669881</v>
+        <v>22.52876063718686</v>
       </c>
       <c r="I24">
-        <v>22.39615813574379</v>
+        <v>22.39615817616497</v>
       </c>
       <c r="J24">
-        <v>22.78753377233469</v>
+        <v>22.78753380698353</v>
       </c>
       <c r="K24">
-        <v>23.41548132489516</v>
+        <v>23.41548162132493</v>
       </c>
       <c r="L24">
-        <v>23.20689482244038</v>
+        <v>23.20689473662167</v>
       </c>
       <c r="M24">
-        <v>23.44891239329111</v>
+        <v>23.44891197518797</v>
       </c>
       <c r="N24">
-        <v>24.08722839111477</v>
+        <v>24.08722734827679</v>
       </c>
       <c r="O24">
-        <v>25.52479685392189</v>
+        <v>25.52479486062217</v>
       </c>
       <c r="P24">
-        <v>26.33302517587888</v>
+        <v>26.33302256452181</v>
       </c>
       <c r="Q24">
-        <v>27.86562119076055</v>
+        <v>27.86561730937759</v>
       </c>
       <c r="R24">
-        <v>29.31889164988896</v>
+        <v>29.31888788456615</v>
       </c>
     </row>
     <row r="25">
@@ -1787,55 +1787,55 @@
         </is>
       </c>
       <c r="B25">
-        <v>23.10395055933318</v>
+        <v>23.1039505528964</v>
       </c>
       <c r="C25">
         <v>36.7783252635105</v>
       </c>
       <c r="D25">
-        <v>23.12280978493632</v>
+        <v>23.12280978439215</v>
       </c>
       <c r="E25">
-        <v>22.18400502747989</v>
+        <v>22.18400503001977</v>
       </c>
       <c r="F25">
-        <v>22.91536405465557</v>
+        <v>22.91536404766341</v>
       </c>
       <c r="G25">
-        <v>22.38397926674374</v>
+        <v>22.38397926856744</v>
       </c>
       <c r="H25">
-        <v>22.69673782817375</v>
+        <v>22.69673783550703</v>
       </c>
       <c r="I25">
-        <v>23.30403114132656</v>
+        <v>23.3040311731857</v>
       </c>
       <c r="J25">
-        <v>24.10625017307588</v>
+        <v>24.10625023224456</v>
       </c>
       <c r="K25">
-        <v>23.96371938544476</v>
+        <v>23.96371956562471</v>
       </c>
       <c r="L25">
-        <v>23.83254692301788</v>
+        <v>23.83254683438264</v>
       </c>
       <c r="M25">
-        <v>23.55238790718725</v>
+        <v>23.5523875034571</v>
       </c>
       <c r="N25">
-        <v>24.07554523007822</v>
+        <v>24.07554451283751</v>
       </c>
       <c r="O25">
-        <v>24.86829506373262</v>
+        <v>24.86829295594557</v>
       </c>
       <c r="P25">
-        <v>26.02991059337381</v>
+        <v>26.02990771753436</v>
       </c>
       <c r="Q25">
-        <v>26.93872134565923</v>
+        <v>26.93871787466788</v>
       </c>
       <c r="R25">
-        <v>28.5320596847988</v>
+        <v>28.53205513758067</v>
       </c>
     </row>
     <row r="26">
@@ -1845,55 +1845,55 @@
         </is>
       </c>
       <c r="B26">
-        <v>22.34732335293532</v>
+        <v>22.34732335445556</v>
       </c>
       <c r="C26">
         <v>36.7783252635105</v>
       </c>
       <c r="D26">
-        <v>22.30135363148166</v>
+        <v>22.30135363288353</v>
       </c>
       <c r="E26">
-        <v>22.18520777390454</v>
+        <v>22.18520777696715</v>
       </c>
       <c r="F26">
-        <v>22.84748787328994</v>
+        <v>22.84748787783845</v>
       </c>
       <c r="G26">
-        <v>22.31813824171928</v>
+        <v>22.318138253444</v>
       </c>
       <c r="H26">
-        <v>22.46450187150302</v>
+        <v>22.46450188786699</v>
       </c>
       <c r="I26">
-        <v>22.32223930888907</v>
+        <v>22.32223934776253</v>
       </c>
       <c r="J26">
-        <v>22.8144850894979</v>
+        <v>22.81448514186631</v>
       </c>
       <c r="K26">
-        <v>23.38720161484682</v>
+        <v>23.38720171240876</v>
       </c>
       <c r="L26">
-        <v>23.52703275077557</v>
+        <v>23.52703260041895</v>
       </c>
       <c r="M26">
-        <v>23.79993766257171</v>
+        <v>23.79993687930419</v>
       </c>
       <c r="N26">
-        <v>24.87009963453895</v>
+        <v>24.87009790334045</v>
       </c>
       <c r="O26">
-        <v>25.91282521422524</v>
+        <v>25.91282289637274</v>
       </c>
       <c r="P26">
-        <v>27.38298967897982</v>
+        <v>27.3829867134353</v>
       </c>
       <c r="Q26">
-        <v>28.7755955531026</v>
+        <v>28.77559183526915</v>
       </c>
       <c r="R26">
-        <v>31.06527910675134</v>
+        <v>31.06527516394339</v>
       </c>
     </row>
     <row r="27">
@@ -1903,55 +1903,55 @@
         </is>
       </c>
       <c r="B27">
-        <v>22.35215611247413</v>
+        <v>22.35215611646589</v>
       </c>
       <c r="C27">
         <v>36.7783252635105</v>
       </c>
       <c r="D27">
-        <v>22.30157349617412</v>
+        <v>22.30157349747331</v>
       </c>
       <c r="E27">
-        <v>22.20382682607948</v>
+        <v>22.20382682928396</v>
       </c>
       <c r="F27">
-        <v>22.82371420737601</v>
+        <v>22.82371421355119</v>
       </c>
       <c r="G27">
-        <v>22.32558878389974</v>
+        <v>22.32558879760621</v>
       </c>
       <c r="H27">
-        <v>22.39579638144877</v>
+        <v>22.3957964039739</v>
       </c>
       <c r="I27">
-        <v>22.28071497695999</v>
+        <v>22.28071503179886</v>
       </c>
       <c r="J27">
-        <v>22.44632122782164</v>
+        <v>22.4463213090462</v>
       </c>
       <c r="K27">
-        <v>22.64181031463891</v>
+        <v>22.64181048248318</v>
       </c>
       <c r="L27">
-        <v>22.41260910898866</v>
+        <v>22.41260947776421</v>
       </c>
       <c r="M27">
-        <v>22.19892778959036</v>
+        <v>22.19892798256673</v>
       </c>
       <c r="N27">
-        <v>22.32572332286126</v>
+        <v>22.32572339827406</v>
       </c>
       <c r="O27">
-        <v>22.79559559298269</v>
+        <v>22.79559579682998</v>
       </c>
       <c r="P27">
-        <v>23.70103606515718</v>
+        <v>23.70103592824402</v>
       </c>
       <c r="Q27">
-        <v>23.90856473092141</v>
+        <v>23.90856403604174</v>
       </c>
       <c r="R27">
-        <v>25.92836574983927</v>
+        <v>25.92836524854777</v>
       </c>
     </row>
     <row r="28">
@@ -1961,55 +1961,55 @@
         </is>
       </c>
       <c r="B28">
-        <v>23.07811272382682</v>
+        <v>23.07811272245921</v>
       </c>
       <c r="C28">
         <v>36.7783252635105</v>
       </c>
       <c r="D28">
-        <v>23.10292601458669</v>
+        <v>23.10292601395267</v>
       </c>
       <c r="E28">
-        <v>22.1687958457596</v>
+        <v>22.16879584831619</v>
       </c>
       <c r="F28">
-        <v>22.9393670277166</v>
+        <v>22.93936702091128</v>
       </c>
       <c r="G28">
-        <v>22.38905495748809</v>
+        <v>22.3890549641112</v>
       </c>
       <c r="H28">
-        <v>22.72166480884211</v>
+        <v>22.72166481164995</v>
       </c>
       <c r="I28">
-        <v>23.20396690573278</v>
+        <v>23.20396691491234</v>
       </c>
       <c r="J28">
-        <v>23.76232632467745</v>
+        <v>23.76232637800928</v>
       </c>
       <c r="K28">
-        <v>23.3289563897113</v>
+        <v>23.32895667976526</v>
       </c>
       <c r="L28">
-        <v>23.27091926680697</v>
+        <v>23.27091946988236</v>
       </c>
       <c r="M28">
-        <v>22.78431922951665</v>
+        <v>22.78431936460346</v>
       </c>
       <c r="N28">
-        <v>22.92552880978287</v>
+        <v>22.92552902164582</v>
       </c>
       <c r="O28">
-        <v>23.32494634071239</v>
+        <v>23.32494639919512</v>
       </c>
       <c r="P28">
-        <v>24.18126527045981</v>
+        <v>24.18126519442607</v>
       </c>
       <c r="Q28">
-        <v>24.37153268814858</v>
+        <v>24.37153260936358</v>
       </c>
       <c r="R28">
-        <v>25.40301731063927</v>
+        <v>25.40301612342529</v>
       </c>
     </row>
     <row r="29">
@@ -2019,55 +2019,55 @@
         </is>
       </c>
       <c r="B29">
-        <v>23.12422564763277</v>
+        <v>23.12422564661435</v>
       </c>
       <c r="C29">
         <v>36.7783252635105</v>
       </c>
       <c r="D29">
-        <v>23.13766284948791</v>
+        <v>23.13766284861809</v>
       </c>
       <c r="E29">
-        <v>22.18571822545039</v>
+        <v>22.1857182278442</v>
       </c>
       <c r="F29">
-        <v>22.93685022581949</v>
+        <v>22.93685021739186</v>
       </c>
       <c r="G29">
-        <v>22.43330731262206</v>
+        <v>22.43330731549799</v>
       </c>
       <c r="H29">
-        <v>22.72690337820855</v>
+        <v>22.72690337279736</v>
       </c>
       <c r="I29">
-        <v>23.18210005271328</v>
+        <v>23.18210006849861</v>
       </c>
       <c r="J29">
-        <v>23.70975639300849</v>
+        <v>23.70975640256009</v>
       </c>
       <c r="K29">
-        <v>23.3897865198733</v>
+        <v>23.38978675089357</v>
       </c>
       <c r="L29">
-        <v>23.36429361901686</v>
+        <v>23.36429378462776</v>
       </c>
       <c r="M29">
-        <v>22.87334430703193</v>
+        <v>22.87334447097446</v>
       </c>
       <c r="N29">
-        <v>22.9376666297534</v>
+        <v>22.93766678346467</v>
       </c>
       <c r="O29">
-        <v>23.17392487504033</v>
+        <v>23.17392480268692</v>
       </c>
       <c r="P29">
-        <v>23.94148146813928</v>
+        <v>23.94148138850845</v>
       </c>
       <c r="Q29">
-        <v>24.00216824627586</v>
+        <v>24.00216807784874</v>
       </c>
       <c r="R29">
-        <v>25.03222995658892</v>
+        <v>25.03222884720771</v>
       </c>
     </row>
     <row r="30">
@@ -2077,55 +2077,55 @@
         </is>
       </c>
       <c r="B30">
-        <v>23.0949280630902</v>
+        <v>23.09492805873664</v>
       </c>
       <c r="C30">
         <v>36.7783252635105</v>
       </c>
       <c r="D30">
-        <v>23.12499079161933</v>
+        <v>23.12499079092073</v>
       </c>
       <c r="E30">
-        <v>22.17598302064018</v>
+        <v>22.17598302318584</v>
       </c>
       <c r="F30">
-        <v>22.8763139492545</v>
+        <v>22.87631394405639</v>
       </c>
       <c r="G30">
-        <v>22.29354175663261</v>
+        <v>22.29354176153176</v>
       </c>
       <c r="H30">
-        <v>22.58634690526145</v>
+        <v>22.58634690599078</v>
       </c>
       <c r="I30">
-        <v>23.00029828461168</v>
+        <v>23.00029830257077</v>
       </c>
       <c r="J30">
-        <v>23.46013340826243</v>
+        <v>23.4601334511463</v>
       </c>
       <c r="K30">
-        <v>23.02558710729859</v>
+        <v>23.02558741791991</v>
       </c>
       <c r="L30">
-        <v>22.97821584141129</v>
+        <v>22.97821599287794</v>
       </c>
       <c r="M30">
-        <v>22.64324094785929</v>
+        <v>22.64324112622071</v>
       </c>
       <c r="N30">
-        <v>22.65983730378849</v>
+        <v>22.65983766850989</v>
       </c>
       <c r="O30">
-        <v>22.81797456001067</v>
+        <v>22.81797462314605</v>
       </c>
       <c r="P30">
-        <v>23.52283342498921</v>
+        <v>23.52283359868993</v>
       </c>
       <c r="Q30">
-        <v>23.62076552206172</v>
+        <v>23.62076665106142</v>
       </c>
       <c r="R30">
-        <v>24.54161534551639</v>
+        <v>24.54161449911298</v>
       </c>
     </row>
     <row r="31">
@@ -2135,55 +2135,55 @@
         </is>
       </c>
       <c r="B31">
-        <v>23.0635181857057</v>
+        <v>23.06351818495921</v>
       </c>
       <c r="C31">
         <v>36.7783252635105</v>
       </c>
       <c r="D31">
-        <v>23.09237591335621</v>
+        <v>23.09237591266093</v>
       </c>
       <c r="E31">
-        <v>22.13641969773129</v>
+        <v>22.13641970011043</v>
       </c>
       <c r="F31">
-        <v>22.84213397951406</v>
+        <v>22.8421339719299</v>
       </c>
       <c r="G31">
-        <v>22.35797457435601</v>
+        <v>22.35797457915665</v>
       </c>
       <c r="H31">
-        <v>22.61439931449411</v>
+        <v>22.61439931833882</v>
       </c>
       <c r="I31">
-        <v>23.05998065341845</v>
+        <v>23.05998064839581</v>
       </c>
       <c r="J31">
-        <v>23.47874864140958</v>
+        <v>23.47874870204986</v>
       </c>
       <c r="K31">
-        <v>23.20341358959199</v>
+        <v>23.20341372600149</v>
       </c>
       <c r="L31">
-        <v>23.25443432846832</v>
+        <v>23.25443432210147</v>
       </c>
       <c r="M31">
-        <v>22.7124263137454</v>
+        <v>22.7124265425091</v>
       </c>
       <c r="N31">
-        <v>22.74481465153961</v>
+        <v>22.74481496315064</v>
       </c>
       <c r="O31">
-        <v>22.86179272575597</v>
+        <v>22.86179289255122</v>
       </c>
       <c r="P31">
-        <v>23.45975811741462</v>
+        <v>23.45975819491585</v>
       </c>
       <c r="Q31">
-        <v>23.62884271489524</v>
+        <v>23.62884271753154</v>
       </c>
       <c r="R31">
-        <v>24.14774686402687</v>
+        <v>24.14774593042727</v>
       </c>
     </row>
     <row r="32">
@@ -2193,55 +2193,55 @@
         </is>
       </c>
       <c r="B32">
-        <v>23.06855621589696</v>
+        <v>23.06855621415826</v>
       </c>
       <c r="C32">
         <v>36.7783252635105</v>
       </c>
       <c r="D32">
-        <v>23.09873993538283</v>
+        <v>23.09873993500754</v>
       </c>
       <c r="E32">
-        <v>22.19014988899618</v>
+        <v>22.19014989208246</v>
       </c>
       <c r="F32">
-        <v>23.01337275266835</v>
+        <v>23.01337274598014</v>
       </c>
       <c r="G32">
-        <v>22.42049522585699</v>
+        <v>22.42049523429369</v>
       </c>
       <c r="H32">
-        <v>22.74127926170976</v>
+        <v>22.74127925383404</v>
       </c>
       <c r="I32">
-        <v>23.30233699698508</v>
+        <v>23.30233707398148</v>
       </c>
       <c r="J32">
-        <v>23.80630375014221</v>
+        <v>23.80630383077156</v>
       </c>
       <c r="K32">
-        <v>23.58064092585175</v>
+        <v>23.58064122834209</v>
       </c>
       <c r="L32">
-        <v>23.4235504592998</v>
+        <v>23.42355067202594</v>
       </c>
       <c r="M32">
-        <v>22.85693124874779</v>
+        <v>22.85693136539301</v>
       </c>
       <c r="N32">
-        <v>22.98295032666232</v>
+        <v>22.98295053594836</v>
       </c>
       <c r="O32">
-        <v>23.49517116439174</v>
+        <v>23.49517091215751</v>
       </c>
       <c r="P32">
-        <v>24.30234390766749</v>
+        <v>24.30234334197547</v>
       </c>
       <c r="Q32">
-        <v>24.21938255778832</v>
+        <v>24.21938150250902</v>
       </c>
       <c r="R32">
-        <v>24.98349557619063</v>
+        <v>24.98349396362487</v>
       </c>
     </row>
     <row r="33">
@@ -2251,55 +2251,55 @@
         </is>
       </c>
       <c r="B33">
-        <v>23.01204755393896</v>
+        <v>23.01204755332362</v>
       </c>
       <c r="C33">
         <v>36.7783252635105</v>
       </c>
       <c r="D33">
-        <v>23.09382497248628</v>
+        <v>23.09382497194248</v>
       </c>
       <c r="E33">
-        <v>22.16579144199038</v>
+        <v>22.16579144444207</v>
       </c>
       <c r="F33">
-        <v>22.86854122785586</v>
+        <v>22.86854122111279</v>
       </c>
       <c r="G33">
-        <v>22.36528517677571</v>
+        <v>22.36528518503347</v>
       </c>
       <c r="H33">
-        <v>22.6697582314455</v>
+        <v>22.66975822584154</v>
       </c>
       <c r="I33">
-        <v>23.22410828784336</v>
+        <v>23.2241082361581</v>
       </c>
       <c r="J33">
-        <v>23.79670428185826</v>
+        <v>23.79670435430469</v>
       </c>
       <c r="K33">
-        <v>23.44443042050235</v>
+        <v>23.44443070704161</v>
       </c>
       <c r="L33">
-        <v>23.24492700441487</v>
+        <v>23.24492702911738</v>
       </c>
       <c r="M33">
-        <v>22.69360688862349</v>
+        <v>22.6936070341827</v>
       </c>
       <c r="N33">
-        <v>22.73110454276448</v>
+        <v>22.73110462813462</v>
       </c>
       <c r="O33">
-        <v>23.1487383750432</v>
+        <v>23.1487382049647</v>
       </c>
       <c r="P33">
-        <v>23.92063030946403</v>
+        <v>23.92062998135043</v>
       </c>
       <c r="Q33">
-        <v>23.93296415029109</v>
+        <v>23.93296357348662</v>
       </c>
       <c r="R33">
-        <v>24.6099725833843</v>
+        <v>24.60997101620473</v>
       </c>
     </row>
     <row r="34">
@@ -2309,55 +2309,55 @@
         </is>
       </c>
       <c r="B34">
-        <v>23.09130738232558</v>
+        <v>23.09130738393918</v>
       </c>
       <c r="C34">
         <v>36.7783252635105</v>
       </c>
       <c r="D34">
-        <v>23.14385577721444</v>
+        <v>23.14385577672535</v>
       </c>
       <c r="E34">
-        <v>22.20066653686231</v>
+        <v>22.20066653993478</v>
       </c>
       <c r="F34">
-        <v>22.97827799673806</v>
+        <v>22.97827799059887</v>
       </c>
       <c r="G34">
-        <v>22.43045238265405</v>
+        <v>22.43045239087701</v>
       </c>
       <c r="H34">
-        <v>22.72927109464134</v>
+        <v>22.72927109858281</v>
       </c>
       <c r="I34">
-        <v>23.14413429725808</v>
+        <v>23.14413431776531</v>
       </c>
       <c r="J34">
-        <v>23.67992236945596</v>
+        <v>23.6799224015592</v>
       </c>
       <c r="K34">
-        <v>23.33379985110889</v>
+        <v>23.33380014428542</v>
       </c>
       <c r="L34">
-        <v>23.22175405843157</v>
+        <v>23.22175427611409</v>
       </c>
       <c r="M34">
-        <v>22.61865561990444</v>
+        <v>22.61865577150324</v>
       </c>
       <c r="N34">
-        <v>22.77387379872762</v>
+        <v>22.77387396502941</v>
       </c>
       <c r="O34">
-        <v>23.19296065383396</v>
+        <v>23.19296067202134</v>
       </c>
       <c r="P34">
-        <v>23.89387665850223</v>
+        <v>23.89387635818347</v>
       </c>
       <c r="Q34">
-        <v>23.76754305592666</v>
+        <v>23.76754248601103</v>
       </c>
       <c r="R34">
-        <v>24.53339379730529</v>
+        <v>24.53339252058725</v>
       </c>
     </row>
     <row r="35">
@@ -2367,55 +2367,55 @@
         </is>
       </c>
       <c r="B35">
-        <v>23.05344953484236</v>
+        <v>23.05344953325911</v>
       </c>
       <c r="C35">
         <v>36.7783252635105</v>
       </c>
       <c r="D35">
-        <v>23.09273363324128</v>
+        <v>23.09273363287555</v>
       </c>
       <c r="E35">
-        <v>22.13753534048172</v>
+        <v>22.13753534335453</v>
       </c>
       <c r="F35">
-        <v>22.8349445490784</v>
+        <v>22.83494454390478</v>
       </c>
       <c r="G35">
-        <v>22.36823806508183</v>
+        <v>22.36823807379821</v>
       </c>
       <c r="H35">
-        <v>22.61175697591824</v>
+        <v>22.61175696360887</v>
       </c>
       <c r="I35">
-        <v>23.076131509712</v>
+        <v>23.07613152593255</v>
       </c>
       <c r="J35">
-        <v>23.4903603366733</v>
+        <v>23.49036038035827</v>
       </c>
       <c r="K35">
-        <v>23.20518528306718</v>
+        <v>23.2051855560693</v>
       </c>
       <c r="L35">
-        <v>23.24232059243287</v>
+        <v>23.24232079756103</v>
       </c>
       <c r="M35">
-        <v>22.69347945702233</v>
+        <v>22.69347957829186</v>
       </c>
       <c r="N35">
-        <v>22.72303875456901</v>
+        <v>22.72303901852915</v>
       </c>
       <c r="O35">
-        <v>23.02511173313541</v>
+        <v>23.02511191446585</v>
       </c>
       <c r="P35">
-        <v>23.7318639833714</v>
+        <v>23.73186416231179</v>
       </c>
       <c r="Q35">
-        <v>23.64715092019183</v>
+        <v>23.6471443082622</v>
       </c>
       <c r="R35">
-        <v>24.28788501507309</v>
+        <v>24.28788398820688</v>
       </c>
     </row>
     <row r="36">
@@ -2425,55 +2425,55 @@
         </is>
       </c>
       <c r="B36">
-        <v>23.0608733011215</v>
+        <v>23.06087330044621</v>
       </c>
       <c r="C36">
         <v>36.7783252635105</v>
       </c>
       <c r="D36">
-        <v>23.11954846358823</v>
+        <v>23.11954846271749</v>
       </c>
       <c r="E36">
-        <v>22.15690426308864</v>
+        <v>22.15690426504289</v>
       </c>
       <c r="F36">
-        <v>22.90270575526258</v>
+        <v>22.90270574745689</v>
       </c>
       <c r="G36">
-        <v>22.39984136577718</v>
+        <v>22.39984136952984</v>
       </c>
       <c r="H36">
-        <v>22.65919051897293</v>
+        <v>22.65919051482775</v>
       </c>
       <c r="I36">
-        <v>23.11785662991304</v>
+        <v>23.11785663730015</v>
       </c>
       <c r="J36">
-        <v>23.65515659834846</v>
+        <v>23.655156616071</v>
       </c>
       <c r="K36">
-        <v>23.30796053739882</v>
+        <v>23.30796076109535</v>
       </c>
       <c r="L36">
-        <v>23.24987827071127</v>
+        <v>23.24987845291415</v>
       </c>
       <c r="M36">
-        <v>22.75017540475999</v>
+        <v>22.750175607453</v>
       </c>
       <c r="N36">
-        <v>22.82311484085613</v>
+        <v>22.82311513941272</v>
       </c>
       <c r="O36">
-        <v>22.87765131376776</v>
+        <v>22.87765114875862</v>
       </c>
       <c r="P36">
-        <v>23.54915873367149</v>
+        <v>23.54915909572239</v>
       </c>
       <c r="Q36">
-        <v>23.59714156663345</v>
+        <v>23.59714153360903</v>
       </c>
       <c r="R36">
-        <v>24.03462809012567</v>
+        <v>24.03462782762035</v>
       </c>
     </row>
     <row r="37">
@@ -2483,55 +2483,55 @@
         </is>
       </c>
       <c r="B37">
-        <v>22.10393742808749</v>
+        <v>22.10393744731806</v>
       </c>
       <c r="C37">
         <v>36.7783252635105</v>
       </c>
       <c r="D37">
-        <v>22.10393742808749</v>
+        <v>22.10393744731806</v>
       </c>
       <c r="E37">
-        <v>22.1663888486286</v>
+        <v>22.16638884199873</v>
       </c>
       <c r="F37">
-        <v>22.18031607616891</v>
+        <v>22.18031609777524</v>
       </c>
       <c r="G37">
-        <v>22.21612206879708</v>
+        <v>22.21612219808565</v>
       </c>
       <c r="H37">
-        <v>23.10877302248595</v>
+        <v>23.10877347893753</v>
       </c>
       <c r="I37">
-        <v>23.89751555269296</v>
+        <v>23.89751614945255</v>
       </c>
       <c r="J37">
-        <v>23.43411622497721</v>
+        <v>23.43411556280579</v>
       </c>
       <c r="K37">
-        <v>23.74122354505201</v>
+        <v>23.74122268414983</v>
       </c>
       <c r="L37">
-        <v>24.09345367917906</v>
+        <v>24.09345128984396</v>
       </c>
       <c r="M37">
-        <v>25.04340009920627</v>
+        <v>25.04339649920679</v>
       </c>
       <c r="N37">
-        <v>26.22389431220714</v>
+        <v>26.22388752831692</v>
       </c>
       <c r="O37">
-        <v>27.67808743736451</v>
+        <v>27.67814648116039</v>
       </c>
       <c r="P37">
-        <v>29.70058004907724</v>
+        <v>29.70061013568963</v>
       </c>
       <c r="Q37">
-        <v>30.93459908890777</v>
+        <v>30.93459211040215</v>
       </c>
       <c r="R37">
-        <v>32.08987709176358</v>
+        <v>32.08986935651145</v>
       </c>
     </row>
     <row r="38">
@@ -2541,55 +2541,55 @@
         </is>
       </c>
       <c r="B38">
-        <v>22.23215319271402</v>
+        <v>22.23215321315867</v>
       </c>
       <c r="C38">
         <v>36.7783252635105</v>
       </c>
       <c r="D38">
-        <v>22.21336832122952</v>
+        <v>22.21336834244824</v>
       </c>
       <c r="E38">
-        <v>22.17668523443627</v>
+        <v>22.1766852474829</v>
       </c>
       <c r="F38">
-        <v>22.09647526464956</v>
+        <v>22.09647529264286</v>
       </c>
       <c r="G38">
-        <v>22.08427348267199</v>
+        <v>22.08427359038169</v>
       </c>
       <c r="H38">
-        <v>22.52052886247612</v>
+        <v>22.5205290081705</v>
       </c>
       <c r="I38">
-        <v>23.00887686894284</v>
+        <v>23.00887721796509</v>
       </c>
       <c r="J38">
-        <v>23.06005852233731</v>
+        <v>23.0600587758778</v>
       </c>
       <c r="K38">
-        <v>23.84738695502346</v>
+        <v>23.84738691778777</v>
       </c>
       <c r="L38">
-        <v>25.49003816192742</v>
+        <v>25.49003830851661</v>
       </c>
       <c r="M38">
-        <v>26.20359534947436</v>
+        <v>26.20359525437953</v>
       </c>
       <c r="N38">
-        <v>26.51943438616479</v>
+        <v>26.51943380052586</v>
       </c>
       <c r="O38">
-        <v>25.9865480000763</v>
+        <v>25.98654663656215</v>
       </c>
       <c r="P38">
-        <v>25.52771206862847</v>
+        <v>25.52770837621152</v>
       </c>
       <c r="Q38">
-        <v>26.02314667278941</v>
+        <v>26.02314051595133</v>
       </c>
       <c r="R38">
-        <v>26.56163101974402</v>
+        <v>26.56162538239185</v>
       </c>
     </row>
     <row r="39">
@@ -2599,55 +2599,55 @@
         </is>
       </c>
       <c r="B39">
-        <v>22.26706264125324</v>
+        <v>22.26706266212441</v>
       </c>
       <c r="C39">
         <v>36.7783252635105</v>
       </c>
       <c r="D39">
-        <v>22.19889393183644</v>
+        <v>22.19889395394818</v>
       </c>
       <c r="E39">
-        <v>22.20897384202701</v>
+        <v>22.20897386016404</v>
       </c>
       <c r="F39">
-        <v>22.0830585136105</v>
+        <v>22.08305856908887</v>
       </c>
       <c r="G39">
-        <v>22.11365606231145</v>
+        <v>22.11365616829987</v>
       </c>
       <c r="H39">
-        <v>22.53470242727872</v>
+        <v>22.53470256303951</v>
       </c>
       <c r="I39">
-        <v>22.94781539556352</v>
+        <v>22.94781572486906</v>
       </c>
       <c r="J39">
-        <v>22.6006244576922</v>
+        <v>22.60062467409398</v>
       </c>
       <c r="K39">
-        <v>23.11285152115039</v>
+        <v>23.11285174176409</v>
       </c>
       <c r="L39">
-        <v>25.11370787950299</v>
+        <v>25.11370797027345</v>
       </c>
       <c r="M39">
-        <v>25.69204040406584</v>
+        <v>25.69204042422135</v>
       </c>
       <c r="N39">
-        <v>26.03864697760438</v>
+        <v>26.03864702093733</v>
       </c>
       <c r="O39">
-        <v>26.2134940584765</v>
+        <v>26.21349400527679</v>
       </c>
       <c r="P39">
-        <v>26.17786053146744</v>
+        <v>26.17785999986748</v>
       </c>
       <c r="Q39">
-        <v>26.20205390017057</v>
+        <v>26.20205264782381</v>
       </c>
       <c r="R39">
-        <v>27.14795566004147</v>
+        <v>27.14795426767785</v>
       </c>
     </row>
     <row r="40">
@@ -2657,55 +2657,55 @@
         </is>
       </c>
       <c r="B40">
-        <v>23.4079131814763</v>
+        <v>23.40791318930587</v>
       </c>
       <c r="C40">
         <v>36.7783252635105</v>
       </c>
       <c r="D40">
-        <v>23.22905148159902</v>
+        <v>23.22905152867819</v>
       </c>
       <c r="E40">
-        <v>23.44885894529377</v>
+        <v>23.44885894198043</v>
       </c>
       <c r="F40">
-        <v>23.89396757822901</v>
+        <v>23.89396749579228</v>
       </c>
       <c r="G40">
-        <v>22.94928918825111</v>
+        <v>22.94928906048966</v>
       </c>
       <c r="H40">
-        <v>22.42719525672033</v>
+        <v>22.42719516422494</v>
       </c>
       <c r="I40">
-        <v>23.24623132458421</v>
+        <v>23.24623127762615</v>
       </c>
       <c r="J40">
-        <v>24.28943689014853</v>
+        <v>24.28943670669189</v>
       </c>
       <c r="K40">
-        <v>25.17663121409698</v>
+        <v>25.17663048031405</v>
       </c>
       <c r="L40">
-        <v>25.66329195775386</v>
+        <v>25.66328996040546</v>
       </c>
       <c r="M40">
-        <v>26.21332004065749</v>
+        <v>26.21331718998603</v>
       </c>
       <c r="N40">
-        <v>27.25224568783856</v>
+        <v>27.25224228647756</v>
       </c>
       <c r="O40">
-        <v>29.18368978238489</v>
+        <v>29.18368603908092</v>
       </c>
       <c r="P40">
-        <v>31.42216677871811</v>
+        <v>31.42216211157808</v>
       </c>
       <c r="Q40">
-        <v>33.43621416102988</v>
+        <v>33.43620723048705</v>
       </c>
       <c r="R40">
-        <v>34.42567943712844</v>
+        <v>34.42567027560303</v>
       </c>
     </row>
     <row r="41">
@@ -2715,55 +2715,55 @@
         </is>
       </c>
       <c r="B41">
-        <v>23.4511212046266</v>
+        <v>23.45112119925905</v>
       </c>
       <c r="C41">
         <v>36.7783252635105</v>
       </c>
       <c r="D41">
-        <v>23.4511212046266</v>
+        <v>23.45112119925905</v>
       </c>
       <c r="E41">
-        <v>22.71667281731481</v>
+        <v>22.71667278343584</v>
       </c>
       <c r="F41">
-        <v>24.35678332323823</v>
+        <v>24.35678320069415</v>
       </c>
       <c r="G41">
-        <v>24.56411763070299</v>
+        <v>24.56411746587215</v>
       </c>
       <c r="H41">
-        <v>24.2469203737808</v>
+        <v>24.24691998367375</v>
       </c>
       <c r="I41">
-        <v>25.54518770789621</v>
+        <v>25.54518700153416</v>
       </c>
       <c r="J41">
-        <v>25.84249731590164</v>
+        <v>25.84249621446489</v>
       </c>
       <c r="K41">
-        <v>26.00556685615377</v>
+        <v>26.00556549214616</v>
       </c>
       <c r="L41">
-        <v>26.67722601777638</v>
+        <v>26.67722423145592</v>
       </c>
       <c r="M41">
-        <v>27.49129475123706</v>
+        <v>27.4912925641121</v>
       </c>
       <c r="N41">
-        <v>28.75411500128819</v>
+        <v>28.75411185753419</v>
       </c>
       <c r="O41">
-        <v>30.85795166708219</v>
+        <v>30.85794737823632</v>
       </c>
       <c r="P41">
-        <v>31.66502699671733</v>
+        <v>31.66502185723201</v>
       </c>
       <c r="Q41">
-        <v>32.48741327160942</v>
+        <v>32.48740728247973</v>
       </c>
       <c r="R41">
-        <v>33.03649388619452</v>
+        <v>33.03648721530396</v>
       </c>
     </row>
     <row r="42">
@@ -2773,55 +2773,55 @@
         </is>
       </c>
       <c r="B42">
-        <v>22.89133441265551</v>
+        <v>22.89133441461042</v>
       </c>
       <c r="C42">
         <v>36.7783252635105</v>
       </c>
       <c r="D42">
-        <v>26.73247845769018</v>
+        <v>26.73247857783609</v>
       </c>
       <c r="E42">
-        <v>22.74894564340975</v>
+        <v>22.74894564017373</v>
       </c>
       <c r="F42">
-        <v>23.82196585209693</v>
+        <v>23.82196580931764</v>
       </c>
       <c r="G42">
-        <v>25.21121173360656</v>
+        <v>25.21121163769594</v>
       </c>
       <c r="H42">
-        <v>24.60869523423765</v>
+        <v>24.60869534753296</v>
       </c>
       <c r="I42">
-        <v>24.16453103198456</v>
+        <v>24.16453136518279</v>
       </c>
       <c r="J42">
-        <v>24.69287891798501</v>
+        <v>24.69287937662958</v>
       </c>
       <c r="K42">
-        <v>26.32009800361815</v>
+        <v>26.32009804195232</v>
       </c>
       <c r="L42">
-        <v>27.9968191173394</v>
+        <v>27.99681972317623</v>
       </c>
       <c r="M42">
-        <v>29.07998822257478</v>
+        <v>29.07998911200184</v>
       </c>
       <c r="N42">
-        <v>29.98350243608951</v>
+        <v>29.98350328116958</v>
       </c>
       <c r="O42">
-        <v>30.5411100833722</v>
+        <v>30.54111166378524</v>
       </c>
       <c r="P42">
-        <v>31.08511648032851</v>
+        <v>31.08511842777281</v>
       </c>
       <c r="Q42">
-        <v>32.02943613560208</v>
+        <v>32.02943873986855</v>
       </c>
       <c r="R42">
-        <v>33.04277862508632</v>
+        <v>33.04278127716891</v>
       </c>
     </row>
     <row r="43">
@@ -2831,55 +2831,55 @@
         </is>
       </c>
       <c r="B43">
-        <v>22.69975939451975</v>
+        <v>22.69975938903599</v>
       </c>
       <c r="C43">
         <v>36.7783252635105</v>
       </c>
       <c r="D43">
-        <v>22.68082301985628</v>
+        <v>22.68082301412029</v>
       </c>
       <c r="E43">
-        <v>23.10884236761735</v>
+        <v>23.108842355873</v>
       </c>
       <c r="F43">
-        <v>23.49929784307953</v>
+        <v>23.49929782059379</v>
       </c>
       <c r="G43">
-        <v>23.2754481981239</v>
+        <v>23.27544819454866</v>
       </c>
       <c r="H43">
-        <v>24.43665044720631</v>
+        <v>24.43665047033842</v>
       </c>
       <c r="I43">
-        <v>24.53316526377354</v>
+        <v>24.53316529333671</v>
       </c>
       <c r="J43">
-        <v>25.23350918494233</v>
+        <v>25.23350919167495</v>
       </c>
       <c r="K43">
-        <v>25.76698196765998</v>
+        <v>25.7669818250428</v>
       </c>
       <c r="L43">
-        <v>26.80709707526522</v>
+        <v>26.80709681272984</v>
       </c>
       <c r="M43">
-        <v>28.23290723267012</v>
+        <v>28.23290704532224</v>
       </c>
       <c r="N43">
-        <v>29.60552968977899</v>
+        <v>29.60552971933608</v>
       </c>
       <c r="O43">
-        <v>30.7043944664307</v>
+        <v>30.70439480869582</v>
       </c>
       <c r="P43">
-        <v>31.10324955762805</v>
+        <v>31.1032497581669</v>
       </c>
       <c r="Q43">
-        <v>31.18145538853662</v>
+        <v>31.18145549051237</v>
       </c>
       <c r="R43">
-        <v>31.5341403794124</v>
+        <v>31.53414017766568</v>
       </c>
     </row>
   </sheetData>
